--- a/outputs/FNX-20260701-004_329_Mount_Rankin_Road.xlsx
+++ b/outputs/FNX-20260701-004_329_Mount_Rankin_Road.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consistency Report" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Takeoff" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Consistency Report" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Takeoff" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -61,8 +61,8 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
-      <color rgb="00C0392B"/>
-      <sz val="10"/>
+      <color rgb="0027AE60"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -71,7 +71,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -86,6 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E8F8F5"/>
+        <bgColor rgb="00E8F8F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FDEDEC"/>
         <bgColor rgb="00FDEDEC"/>
       </patternFill>
@@ -94,6 +100,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F7FD"/>
         <bgColor rgb="00F2F7FD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2FDF8"/>
+        <bgColor rgb="00F2FDF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -123,7 +135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -144,18 +156,29 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -523,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -581,7 +604,7 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -592,7 +615,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -604,7 +627,7 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>REJECTED (Low Quality)</t>
+          <t>PASSED</t>
         </is>
       </c>
     </row>
@@ -635,306 +658,17 @@
     <row r="14" ht="20" customHeight="1">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>W13</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C14" s="10" t="inlineStr">
-        <is>
-          <t>W13 (Kitchen/Living1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>W14</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C15" s="10" t="inlineStr">
-        <is>
-          <t>W14 (Kitchen/Living1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>W18</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C16" s="10" t="inlineStr">
-        <is>
-          <t>W18 (Kitchen/Living1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C17" s="10" t="inlineStr">
-        <is>
-          <t>W4 (Kitchen/Living1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C18" s="10" t="inlineStr">
-        <is>
-          <t>W5 (Kitchen/Living1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C19" s="10" t="inlineStr">
-        <is>
-          <t>W6 (Kitchen/Living1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>W12</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C20" s="10" t="inlineStr">
-        <is>
-          <t>W12 (Living 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>W17</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>W17 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C22" s="10" t="inlineStr">
-        <is>
-          <t>W1 (Bedroom 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>W16</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C23" s="10" t="inlineStr">
-        <is>
-          <t>W16 (Night Time 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C24" s="10" t="inlineStr">
-        <is>
-          <t>W2 (Night Time 2) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>W11</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C25" s="10" t="inlineStr">
-        <is>
-          <t>W11 (Bedroom 2) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>W10</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C26" s="10" t="inlineStr">
-        <is>
-          <t>W10 (Bedroom 3) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>W9</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C27" s="10" t="inlineStr">
-        <is>
-          <t>W9 (Bedroom 4) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C28" s="10" t="inlineStr">
-        <is>
-          <t>W3 (Unconditioned 1) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="6" t="inlineStr">
-        <is>
-          <t>W7</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C29" s="10" t="inlineStr">
-        <is>
-          <t>W7 (Unconditioned 2) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>W8</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C30" s="10" t="inlineStr">
-        <is>
-          <t>W8 (Unconditioned 3) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="6" t="inlineStr">
-        <is>
-          <t>W15</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Missing in Plans</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>W15 (Day Time 4) listed in NatHERS but not found on floor plans. Verify location on drawings.</t>
+          <t>Plans</t>
+        </is>
+      </c>
+      <c r="B14" s="10" t="inlineStr">
+        <is>
+          <t>Info</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>No plan documents were supplied in this submission. Glazing takeoff is based entirely on the NatHERS certificate schedule.</t>
         </is>
       </c>
     </row>
@@ -958,12 +692,12 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="34" customWidth="1" min="7" max="7"/>
+    <col width="51" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -1054,24 +788,24 @@
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>Sliding</t>
-        </is>
-      </c>
-      <c r="F3" s="14" t="inlineStr"/>
+          <t>sliding</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
-          <t>Aluminium B DG Argon Fill High</t>
-        </is>
-      </c>
-      <c r="H3" s="14" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="I3" s="14" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
+          <t>Aluminium B DG Argon Fill High Solar Gain low-E</t>
+        </is>
+      </c>
+      <c r="H3" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I3" s="14" t="n">
+        <v>0.52</v>
       </c>
       <c r="J3" s="13" t="inlineStr">
         <is>
@@ -1083,59 +817,59 @@
       </c>
       <c r="L3" s="13" t="inlineStr">
         <is>
-          <t>Plans / NatHERS</t>
+          <t>NatHERS p.5, p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>Kitchen/Living1</t>
         </is>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="17" t="inlineStr">
         <is>
           <t>W14</t>
         </is>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="18" t="n">
         <v>2100</v>
       </c>
-      <c r="D4" s="15" t="n">
+      <c r="D4" s="18" t="n">
         <v>4200</v>
       </c>
-      <c r="E4" s="13" t="inlineStr">
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>sliding</t>
         </is>
       </c>
-      <c r="F4" s="14" t="inlineStr"/>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>Aluminium B DG Argon Fill High</t>
-        </is>
-      </c>
-      <c r="H4" s="14" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="I4" s="14" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="J4" s="13" t="inlineStr">
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="16" t="inlineStr">
+        <is>
+          <t>Aluminium B DG Argon Fill High Solar Gain low-E</t>
+        </is>
+      </c>
+      <c r="H4" s="17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I4" s="17" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J4" s="16" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K4" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="13" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="K4" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="16" t="inlineStr">
+        <is>
+          <t>NatHERS p.5, p.6, p.7</t>
         </is>
       </c>
     </row>
@@ -1161,21 +895,21 @@
           <t>fixed</t>
         </is>
       </c>
-      <c r="F5" s="14" t="inlineStr"/>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>Aluminium B DG Argon Fill High</t>
-        </is>
-      </c>
-      <c r="H5" s="14" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
+          <t>Aluminium B DG Argon Fill High Solar Gain low-E</t>
+        </is>
+      </c>
+      <c r="H5" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I5" s="14" t="n">
+        <v>0.52</v>
       </c>
       <c r="J5" s="13" t="inlineStr">
         <is>
@@ -1187,7 +921,7 @@
       </c>
       <c r="L5" s="13" t="inlineStr">
         <is>
-          <t>Plans / NatHERS</t>
+          <t>NatHERS p.5, p.6, p.7</t>
         </is>
       </c>
     </row>
@@ -1213,21 +947,21 @@
           <t>sliding</t>
         </is>
       </c>
-      <c r="F6" s="14" t="inlineStr"/>
+      <c r="F6" s="14" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Aluminium B DG Argon Fill High</t>
-        </is>
-      </c>
-      <c r="H6" s="14" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
+          <t>Aluminium B DG Argon Fill High Solar Gain low-E</t>
+        </is>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>0.52</v>
       </c>
       <c r="J6" s="13" t="inlineStr">
         <is>
@@ -1239,7 +973,7 @@
       </c>
       <c r="L6" s="13" t="inlineStr">
         <is>
-          <t>Plans / NatHERS</t>
+          <t>NatHERS p.5, p.6, p.7</t>
         </is>
       </c>
     </row>
@@ -1265,21 +999,21 @@
           <t>sliding</t>
         </is>
       </c>
-      <c r="F7" s="14" t="inlineStr"/>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>Aluminium B DG Argon Fill High</t>
-        </is>
-      </c>
-      <c r="H7" s="14" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
+          <t>Aluminium B DG Argon Fill High Solar Gain low-E</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0.52</v>
       </c>
       <c r="J7" s="13" t="inlineStr">
         <is>
@@ -1291,59 +1025,59 @@
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
-          <t>Plans / NatHERS</t>
+          <t>NatHERS p.5, p.6, p.7</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="16" t="inlineStr">
         <is>
           <t>Kitchen/Living1</t>
         </is>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="18" t="n">
         <v>2100</v>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="18" t="n">
         <v>2400</v>
       </c>
-      <c r="E8" s="13" t="inlineStr">
+      <c r="E8" s="16" t="inlineStr">
         <is>
           <t>sliding</t>
         </is>
       </c>
-      <c r="F8" s="14" t="inlineStr"/>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>Aluminium B DG Argon Fill High</t>
-        </is>
-      </c>
-      <c r="H8" s="14" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="J8" s="13" t="inlineStr">
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>Aluminium B DG Argon Fill High Solar Gain low-E</t>
+        </is>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J8" s="16" t="inlineStr">
         <is>
           <t>Aluminium</t>
         </is>
       </c>
-      <c r="K8" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" s="13" t="inlineStr">
-        <is>
-          <t>Plans / NatHERS</t>
+      <c r="K8" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="16" t="inlineStr">
+        <is>
+          <t>NatHERS p.5, p.6, p.7</t>
         </is>
       </c>
     </row>
@@ -1369,21 +1103,21 @@
           <t>sliding</t>
         </is>
       </c>
-      <c r="F9" s="14" t="inlineStr"/>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>Aluminium B DG Argon Fill High</t>
-        </is>
-      </c>
-      <c r="H9" s="14" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
+          <t>Aluminium B DG Argon Fill High Solar Gain low-E</t>
+        </is>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0.52</v>
       </c>
       <c r="J9" s="13" t="inlineStr">
         <is>
@@ -1395,7 +1129,7 @@
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
-          <t>Plans / NatHERS</t>
+          <t>NatHERS p.5, p.6, p.7</t>
         </is>
       </c>
     </row>
@@ -1421,21 +1155,21 @@
           <t>sliding</t>
         </is>
       </c>
-      <c r="F10" s="14" t="inlineStr"/>
+      <c r="F10" s="14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>Aluminium B DG Argon Fill High</t>
-        </is>
-      </c>
-      <c r="H10" s="14" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="I10" s="14" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
+          <t>Aluminium B DG Argon Fill High Solar Gain low-E</t>
+        </is>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>0.52</v>
       </c>
       <c r="J10" s="13" t="inlineStr">
         <is>
@@ -1447,7 +1181,7 @@
       </c>
       <c r="L10" s="13" t="inlineStr">
         <is>
-          <t>Plans / NatHERS</t>
+          <t>NatHERS p.5, p.6, p.7</t>
         </is>
       </c>
     </row>
@@ -1473,21 +1207,21 @@
           <t>sliding</t>
         </is>
       </c>
-      <c r="F11" s="14" t="inlineStr"/>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>Aluminium B DG Argon Fill High</t>
-        </is>
-      </c>
-      <c r="H11" s="14" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
+          <t>Aluminium B DG Argon Fill High Solar Gain low-E</t>
+        </is>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>0.52</v>
       </c>
       <c r="J11" s="13" t="inlineStr">
         <is>
@@ -1499,7 +1233,7 @@
       </c>
       <c r="L11" s="13" t="inlineStr">
         <is>
-          <t>Plans / NatHERS</t>
+          <t>NatHERS p.5, p.6, p.7</t>
         </is>
       </c>
     </row>
@@ -1525,21 +1259,21 @@
           <t>sliding</t>
         </is>
       </c>
-      <c r="F12" s="14" t="inlineStr"/>
+      <c r="F12" s="14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>Aluminium B DG Argon Fill High</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
+          <t>Aluminium B DG Argon Fill High Solar Gain low-E</t>
+        </is>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>0.52</v>
       </c>
       <c r="J12" s="13" t="inlineStr">
         <is>
@@ -1551,7 +1285,7 @@
       </c>
       <c r="L12" s="13" t="inlineStr">
         <is>
-          <t>Plans / NatHERS</t>
+          <t>NatHERS p.5, p.6, p.7</t>
         </is>
       </c>
     </row>
@@ -1577,21 +1311,21 @@
           <t>sliding</t>
         </is>
       </c>
-      <c r="F13" s="14" t="inlineStr"/>
+      <c r="F13" s="14" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>Aluminium B DG Argon Fill High</t>
-        </is>
-      </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
+          <t>Aluminium B DG Argon Fill High Solar Gain low-E</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>0.52</v>
       </c>
       <c r="J13" s="13" t="inlineStr">
         <is>
@@ -1603,7 +1337,7 @@
       </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
-          <t>Plans / NatHERS</t>
+          <t>NatHERS p.5, p.6, p.7</t>
         </is>
       </c>
     </row>
@@ -1629,21 +1363,21 @@
           <t>sliding</t>
         </is>
       </c>
-      <c r="F14" s="14" t="inlineStr"/>
+      <c r="F14" s="14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>Aluminium B DG Argon Fill High</t>
-        </is>
-      </c>
-      <c r="H14" s="14" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="I14" s="14" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
+          <t>Aluminium B DG Argon Fill High Solar Gain low-E</t>
+        </is>
+      </c>
+      <c r="H14" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I14" s="14" t="n">
+        <v>0.52</v>
       </c>
       <c r="J14" s="13" t="inlineStr">
         <is>
@@ -1655,7 +1389,7 @@
       </c>
       <c r="L14" s="13" t="inlineStr">
         <is>
-          <t>Plans / NatHERS</t>
+          <t>NatHERS p.5, p.6, p.7</t>
         </is>
       </c>
     </row>
@@ -1681,21 +1415,21 @@
           <t>sliding</t>
         </is>
       </c>
-      <c r="F15" s="14" t="inlineStr"/>
+      <c r="F15" s="14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>Aluminium B DG Argon Fill High</t>
-        </is>
-      </c>
-      <c r="H15" s="14" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="I15" s="14" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
+          <t>Aluminium B DG Argon Fill High Solar Gain low-E</t>
+        </is>
+      </c>
+      <c r="H15" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I15" s="14" t="n">
+        <v>0.52</v>
       </c>
       <c r="J15" s="13" t="inlineStr">
         <is>
@@ -1707,7 +1441,7 @@
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>Plans / NatHERS</t>
+          <t>NatHERS p.5, p.6, p.7</t>
         </is>
       </c>
     </row>
@@ -1733,21 +1467,21 @@
           <t>sliding</t>
         </is>
       </c>
-      <c r="F16" s="14" t="inlineStr"/>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>Aluminium B DG Argon Fill High</t>
-        </is>
-      </c>
-      <c r="H16" s="14" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="I16" s="14" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
+          <t>Aluminium B DG Argon Fill High Solar Gain low-E</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>0.52</v>
       </c>
       <c r="J16" s="13" t="inlineStr">
         <is>
@@ -1759,7 +1493,7 @@
       </c>
       <c r="L16" s="13" t="inlineStr">
         <is>
-          <t>Plans / NatHERS</t>
+          <t>NatHERS p.5, p.6, p.7</t>
         </is>
       </c>
     </row>
@@ -1785,21 +1519,21 @@
           <t>sliding</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr"/>
+      <c r="F17" s="14" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>Aluminium B DG Argon Fill High</t>
-        </is>
-      </c>
-      <c r="H17" s="14" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="I17" s="14" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
+          <t>Aluminium B DG Argon Fill High Solar Gain low-E</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>0.52</v>
       </c>
       <c r="J17" s="13" t="inlineStr">
         <is>
@@ -1811,7 +1545,7 @@
       </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
-          <t>Plans / NatHERS</t>
+          <t>NatHERS p.5, p.6, p.7</t>
         </is>
       </c>
     </row>
@@ -1837,21 +1571,21 @@
           <t>sliding</t>
         </is>
       </c>
-      <c r="F18" s="14" t="inlineStr"/>
+      <c r="F18" s="14" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>Aluminium B DG Argon Fill High</t>
-        </is>
-      </c>
-      <c r="H18" s="14" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="I18" s="14" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
+          <t>Aluminium B DG Argon Fill High Solar Gain low-E</t>
+        </is>
+      </c>
+      <c r="H18" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <v>0.52</v>
       </c>
       <c r="J18" s="13" t="inlineStr">
         <is>
@@ -1863,7 +1597,7 @@
       </c>
       <c r="L18" s="13" t="inlineStr">
         <is>
-          <t>Plans / NatHERS</t>
+          <t>NatHERS p.5, p.6, p.7</t>
         </is>
       </c>
     </row>
@@ -1889,21 +1623,21 @@
           <t>sliding</t>
         </is>
       </c>
-      <c r="F19" s="14" t="inlineStr"/>
+      <c r="F19" s="14" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>Aluminium B DG Argon Fill High</t>
-        </is>
-      </c>
-      <c r="H19" s="14" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="I19" s="14" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
+          <t>Aluminium B DG Argon Fill High Solar Gain low-E</t>
+        </is>
+      </c>
+      <c r="H19" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <v>0.52</v>
       </c>
       <c r="J19" s="13" t="inlineStr">
         <is>
@@ -1915,7 +1649,7 @@
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
-          <t>Plans / NatHERS</t>
+          <t>NatHERS p.5, p.6, p.7</t>
         </is>
       </c>
     </row>
@@ -1941,21 +1675,21 @@
           <t>sliding</t>
         </is>
       </c>
-      <c r="F20" s="14" t="inlineStr"/>
+      <c r="F20" s="14" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>Aluminium B DG Argon Fill High</t>
-        </is>
-      </c>
-      <c r="H20" s="14" t="inlineStr">
-        <is>
-          <t>4.1</t>
-        </is>
-      </c>
-      <c r="I20" s="14" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
+          <t>Aluminium B DG Argon Fill High Solar Gain low-E</t>
+        </is>
+      </c>
+      <c r="H20" s="14" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <v>0.52</v>
       </c>
       <c r="J20" s="13" t="inlineStr">
         <is>
@@ -1967,7 +1701,7 @@
       </c>
       <c r="L20" s="13" t="inlineStr">
         <is>
-          <t>Plans / NatHERS</t>
+          <t>NatHERS p.5, p.6, p.7</t>
         </is>
       </c>
     </row>

--- a/outputs/FNX-20260701-004_329_Mount_Rankin_Road.xlsx
+++ b/outputs/FNX-20260701-004_329_Mount_Rankin_Road.xlsx
@@ -668,7 +668,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>No plan documents were supplied in this submission. Glazing takeoff is based entirely on the NatHERS certificate schedule.</t>
+          <t>Floor plans were supplied, but no readable layout or schedule could be processed (e.g. image-only sheets). Glazing takeoff is based entirely on the NatHERS certificate schedule.</t>
         </is>
       </c>
     </row>
